--- a/exports/trend_1d/MAXHEALTH_full_report.xlsx
+++ b/exports/trend_1d/MAXHEALTH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>23.16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44480</v>
+        <v>44481</v>
       </c>
       <c r="H2" t="n">
-        <v>348.35</v>
+        <v>335.7</v>
       </c>
       <c r="I2" t="n">
         <v>347.4422157402912</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
-        <v>202.26</v>
+        <v>191.28</v>
       </c>
       <c r="L2" t="n">
         <v>15.7</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>274</v>
+        <v>275</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H3" t="n">
-        <v>364.95</v>
+        <v>371.75</v>
       </c>
       <c r="I3" t="n">
         <v>369.310915092092</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.710000000000001</v>
+        <v>-10.74</v>
       </c>
       <c r="L3" t="n">
         <v>12.3</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.4</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H4" t="n">
-        <v>390.95</v>
+        <v>384.7</v>
       </c>
       <c r="I4" t="n">
         <v>388.8219811294109</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>5.16</v>
+        <v>3.48</v>
       </c>
       <c r="L4" t="n">
         <v>8.619999999999999</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H5" t="n">
-        <v>354.5</v>
+        <v>369.4</v>
       </c>
       <c r="I5" t="n">
         <v>369.1687405297681</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K5" t="n">
-        <v>7.85</v>
+        <v>3.98</v>
       </c>
       <c r="L5" t="n">
         <v>2.21</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>12.03</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H6" t="n">
-        <v>373.9</v>
+        <v>365.25</v>
       </c>
       <c r="I6" t="n">
         <v>366.6926267295871</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>1.22</v>
+        <v>-1.12</v>
       </c>
       <c r="L6" t="n">
         <v>6.82</v>
       </c>
       <c r="M6" t="n">
-        <v>1.41</v>
+        <v>2.78</v>
       </c>
       <c r="N6" t="n">
         <v>6.1</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>15.61</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H7" t="n">
-        <v>361.9</v>
+        <v>396.85</v>
       </c>
       <c r="I7" t="n">
         <v>386.7125146105048</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K7" t="n">
-        <v>0.92</v>
+        <v>-8.65</v>
       </c>
       <c r="L7" t="n">
-        <v>8.41</v>
+        <v>10.83</v>
       </c>
       <c r="M7" t="n">
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>4.09</v>
+        <v>9.66</v>
       </c>
       <c r="O7" t="n">
         <v>-2.31</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>15.79</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H8" t="n">
-        <v>441.1</v>
+        <v>432.7</v>
       </c>
       <c r="I8" t="n">
         <v>435.3233365670163</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K8" t="n">
-        <v>11.15</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>10.77</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H9" t="n">
-        <v>450.9</v>
+        <v>479</v>
       </c>
       <c r="I9" t="n">
         <v>460.5704563956152</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.21</v>
+        <v>-10.7</v>
       </c>
       <c r="L9" t="n">
-        <v>6.29</v>
+        <v>12.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.34</v>
       </c>
       <c r="N9" t="n">
-        <v>2.67</v>
+        <v>6.23</v>
       </c>
       <c r="O9" t="n">
         <v>-1.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>14.88</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H10" t="n">
-        <v>572.3</v>
+        <v>571.2</v>
       </c>
       <c r="I10" t="n">
         <v>571.261467210634</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K10" t="n">
-        <v>19.48</v>
+        <v>19.25</v>
       </c>
       <c r="L10" t="n">
         <v>9.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.34</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H11" t="n">
-        <v>575.35</v>
+        <v>589.55</v>
       </c>
       <c r="I11" t="n">
         <v>584.5822757578539</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.73</v>
+        <v>-3.21</v>
       </c>
       <c r="L11" t="n">
-        <v>3.63</v>
+        <v>4.87</v>
       </c>
       <c r="M11" t="n">
         <v>1.27</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45187</v>
+        <v>45189</v>
       </c>
       <c r="H12" t="n">
-        <v>574.4</v>
+        <v>554.15</v>
       </c>
       <c r="I12" t="n">
         <v>557.7874980014352</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.57</v>
+        <v>-6</v>
       </c>
       <c r="L12" t="n">
-        <v>4.06</v>
+        <v>6.5</v>
       </c>
       <c r="M12" t="n">
         <v>1.2</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H13" t="n">
-        <v>599.15</v>
+        <v>615.4</v>
       </c>
       <c r="I13" t="n">
         <v>611.0273381271573</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.119999999999999</v>
+        <v>-11.05</v>
       </c>
       <c r="L13" t="n">
-        <v>9.9</v>
+        <v>11.87</v>
       </c>
       <c r="M13" t="n">
         <v>1.78</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.85</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="H14" t="n">
-        <v>793.35</v>
+        <v>736.75</v>
       </c>
       <c r="I14" t="n">
         <v>781.087975039258</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K14" t="n">
-        <v>28.92</v>
+        <v>19.72</v>
       </c>
       <c r="L14" t="n">
         <v>2.64</v>
@@ -1239,7 +1406,7 @@
         <v>4.89</v>
       </c>
       <c r="N14" t="n">
-        <v>6.83</v>
+        <v>7.13</v>
       </c>
       <c r="O14" t="n">
         <v>2.71</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>18.13</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H15" t="n">
-        <v>820.55</v>
+        <v>828.4</v>
       </c>
       <c r="I15" t="n">
         <v>823.0890903816424</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.37</v>
+        <v>-12.44</v>
       </c>
       <c r="L15" t="n">
-        <v>13.12</v>
+        <v>13.18</v>
       </c>
       <c r="M15" t="n">
         <v>4.11</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H16" t="n">
-        <v>817.95</v>
+        <v>778.1</v>
       </c>
       <c r="I16" t="n">
         <v>785.6009767943272</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.26</v>
+        <v>-6.07</v>
       </c>
       <c r="L16" t="n">
-        <v>2.51</v>
+        <v>7.05</v>
       </c>
       <c r="M16" t="n">
         <v>1.77</v>
       </c>
       <c r="N16" t="n">
-        <v>4.26</v>
+        <v>4.87</v>
       </c>
       <c r="O16" t="n">
         <v>0.96</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>15.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H17" t="n">
-        <v>802.5</v>
+        <v>870.5</v>
       </c>
       <c r="I17" t="n">
         <v>852.1589633409715</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.14</v>
+        <v>-11.88</v>
       </c>
       <c r="L17" t="n">
-        <v>11.49</v>
+        <v>12.81</v>
       </c>
       <c r="M17" t="n">
         <v>1.5</v>
       </c>
       <c r="N17" t="n">
-        <v>6.63</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>-4.87</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.01</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H18" t="n">
-        <v>942.15</v>
+        <v>926.35</v>
       </c>
       <c r="I18" t="n">
         <v>927.7762335432853</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K18" t="n">
-        <v>8.23</v>
+        <v>6.42</v>
       </c>
       <c r="L18" t="n">
         <v>7.24</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>13.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="H19" t="n">
-        <v>992.35</v>
+        <v>1017.6</v>
       </c>
       <c r="I19" t="n">
         <v>994.909433990548</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.12</v>
+        <v>-9.85</v>
       </c>
       <c r="L19" t="n">
-        <v>7.84</v>
+        <v>10.54</v>
       </c>
       <c r="M19" t="n">
         <v>1.39</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.25</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H20" t="n">
-        <v>999.95</v>
+        <v>971.75</v>
       </c>
       <c r="I20" t="n">
         <v>980.8867271221518</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.73</v>
+        <v>-4.51</v>
       </c>
       <c r="L20" t="n">
         <v>7.99</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H21" t="n">
-        <v>1064.25</v>
+        <v>1096.9</v>
       </c>
       <c r="I21" t="n">
         <v>1094.621583201538</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.52</v>
+        <v>-12.88</v>
       </c>
       <c r="L21" t="n">
-        <v>9.800000000000001</v>
+        <v>13.82</v>
       </c>
       <c r="M21" t="n">
         <v>1.5</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.87</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H22" t="n">
-        <v>1149.9</v>
+        <v>1082.45</v>
       </c>
       <c r="I22" t="n">
         <v>1086.979068729456</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>4.83</v>
+        <v>-1.32</v>
       </c>
       <c r="L22" t="n">
         <v>3.18</v>
@@ -1695,7 +1958,7 @@
         <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>4.86</v>
+        <v>5.87</v>
       </c>
       <c r="O22" t="n">
         <v>3.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>14.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45689</v>
+        <v>45691</v>
       </c>
       <c r="H23" t="n">
-        <v>1108.25</v>
+        <v>1145</v>
       </c>
       <c r="I23" t="n">
         <v>1140.443436287354</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.38</v>
+        <v>-5.78</v>
       </c>
       <c r="L23" t="n">
-        <v>4.16</v>
+        <v>6.24</v>
       </c>
       <c r="M23" t="n">
         <v>1.84</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>14.17</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H24" t="n">
-        <v>1071.85</v>
+        <v>1019.95</v>
       </c>
       <c r="I24" t="n">
         <v>1049.662606988411</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.39</v>
+        <v>-10.92</v>
       </c>
       <c r="L24" t="n">
-        <v>6.99</v>
+        <v>11.18</v>
       </c>
       <c r="M24" t="n">
         <v>0.28</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>17.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H25" t="n">
-        <v>1016.95</v>
+        <v>1087.45</v>
       </c>
       <c r="I25" t="n">
         <v>1085.836830248266</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" t="n">
-        <v>0.29</v>
+        <v>-6.62</v>
       </c>
       <c r="L25" t="n">
-        <v>5.69</v>
+        <v>7.01</v>
       </c>
       <c r="M25" t="n">
         <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.54</v>
+        <v>6.93</v>
       </c>
       <c r="O25" t="n">
         <v>-4.84</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.63</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="H26" t="n">
-        <v>1221.4</v>
+        <v>1183.4</v>
       </c>
       <c r="I26" t="n">
         <v>1199.455685455383</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K26" t="n">
-        <v>12.32</v>
+        <v>8.82</v>
       </c>
       <c r="L26" t="n">
         <v>5.74</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.93</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="H27" t="n">
-        <v>1155.8</v>
+        <v>1175.3</v>
       </c>
       <c r="I27" t="n">
         <v>1167.230590995077</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K27" t="n">
-        <v>2.33</v>
+        <v>0.68</v>
       </c>
       <c r="L27" t="n">
         <v>2.91</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>7.58</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H28" t="n">
-        <v>1138.4</v>
+        <v>1125.4</v>
       </c>
       <c r="I28" t="n">
         <v>1131.820955422595</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.14</v>
+        <v>-4.25</v>
       </c>
       <c r="L28" t="n">
-        <v>3.95</v>
+        <v>4.83</v>
       </c>
       <c r="M28" t="n">
-        <v>0.91</v>
+        <v>1.7</v>
       </c>
       <c r="N28" t="n">
         <v>2.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.18</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H29" t="n">
-        <v>1168.9</v>
+        <v>1181.1</v>
       </c>
       <c r="I29" t="n">
         <v>1174.567808246326</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.87</v>
+        <v>-4.95</v>
       </c>
       <c r="L29" t="n">
-        <v>4.14</v>
+        <v>5.2</v>
       </c>
       <c r="M29" t="n">
         <v>2.69</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.51</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H30" t="n">
-        <v>1097.4</v>
+        <v>1079.4</v>
       </c>
       <c r="I30" t="n">
         <v>1080.571618337389</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.09</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>9.4</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.5</v>
+        <v>1025.45</v>
       </c>
       <c r="I31" t="n">
         <v>1022.895960876881</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K31" t="n">
-        <v>7.03</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
         <v>2.73</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.21</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H32" t="n">
-        <v>1032.2</v>
+        <v>1020.4</v>
       </c>
       <c r="I32" t="n">
         <v>1026.121406234949</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>0.66</v>
+        <v>-0.49</v>
       </c>
       <c r="L32" t="n">
         <v>2.86</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.82</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H33" t="n">
-        <v>990.65</v>
+        <v>1007.65</v>
       </c>
       <c r="I33" t="n">
         <v>1005.874502388821</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="L33" t="n">
         <v>1.1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="H34" t="n">
-        <v>1023.25</v>
+        <v>1000.85</v>
       </c>
       <c r="I34" t="n">
         <v>1010.203612483058</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K34" t="n">
-        <v>1.55</v>
+        <v>-0.67</v>
       </c>
       <c r="L34" t="n">
         <v>7.21</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.17</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H35" t="n">
-        <v>1026.15</v>
+        <v>1090.45</v>
       </c>
       <c r="I35" t="n">
         <v>1034.982197583052</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.53</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>3.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>1.13</v>
       </c>
       <c r="N35" t="n">
-        <v>3.09</v>
+        <v>6.27</v>
       </c>
       <c r="O35" t="n">
         <v>-2.19</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H36" t="n">
-        <v>1069</v>
+        <v>1040</v>
       </c>
       <c r="I36" t="n">
         <v>1057.866466690234</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.97</v>
+        <v>-4.63</v>
       </c>
       <c r="L36" t="n">
         <v>5.86</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.57</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H37" t="n">
-        <v>1049.3</v>
+        <v>1066.6</v>
       </c>
       <c r="I37" t="n">
         <v>1058.558191975879</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.89</v>
+        <v>-2.56</v>
       </c>
       <c r="L37" t="n">
-        <v>2.63</v>
+        <v>3.13</v>
       </c>
       <c r="M37" t="n">
         <v>0.99</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.94</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H38" t="n">
-        <v>1000.1</v>
+        <v>982.1</v>
       </c>
       <c r="I38" t="n">
         <v>994.8660153228224</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.23</v>
+        <v>-7.92</v>
       </c>
       <c r="L38" t="n">
-        <v>7.27</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>2.35</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2667,6 +3134,14 @@
       <c r="Q39" t="n">
         <v>20</v>
       </c>
+      <c r="R39" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5347,7 +5822,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.4</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="6">
@@ -5357,7 +5832,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -5367,7 +5842,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8">
@@ -5377,7 +5852,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5387,7 +5862,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -5397,7 +5872,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111.8</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="11">
@@ -5407,7 +5882,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -5417,7 +5892,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -5427,7 +5902,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="14">
@@ -5437,7 +5912,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.06</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="15">
@@ -5447,7 +5922,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.97</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="16">
@@ -5457,7 +5932,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.29</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="17">
@@ -5467,7 +5942,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>202.26</v>
+        <v>191.28</v>
       </c>
     </row>
     <row r="18">
@@ -5477,7 +5952,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="19">
@@ -5487,7 +5962,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.48</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="20">
@@ -5497,7 +5972,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.29</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="21">
@@ -5517,7 +5992,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -5527,7 +6002,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5537,7 +6012,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="25">
@@ -5557,7 +6032,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="27">
@@ -5567,7 +6042,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.390000000000001</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="28">
@@ -5577,7 +6052,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
